--- a/data/trans_camb/PCS12_SP_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 2,5</t>
+          <t>-11,07; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 0,45</t>
+          <t>-12,07; 1,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 11,98</t>
+          <t>-1,66; 11,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 3,23</t>
+          <t>-14,39; 2,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,67; -6,54</t>
+          <t>-23,09; -7,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 1,21</t>
+          <t>-12,21; 1,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 0,64</t>
+          <t>-9,83; 0,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,01; -4,88</t>
+          <t>-14,17; -4,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 5,38</t>
+          <t>-3,71; 5,9</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 6,61</t>
+          <t>-24,85; 8,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 1,11</t>
+          <t>-27,73; 3,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 31,17</t>
+          <t>-3,73; 30,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 7,85</t>
+          <t>-27,22; 5,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,54; -14,81</t>
+          <t>-44,94; -17,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 3,15</t>
+          <t>-23,38; 2,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 1,63</t>
+          <t>-21,35; 1,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,78; -11,54</t>
+          <t>-31,03; -10,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 12,85</t>
+          <t>-8,16; 14,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 12,02</t>
+          <t>-2,3; 12,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 0,8</t>
+          <t>-13,86; 1,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 11,08</t>
+          <t>-3,58; 10,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 8,12</t>
+          <t>-7,32; 7,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 4,42</t>
+          <t>-10,38; 4,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 10,62</t>
+          <t>-1,96; 11,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 8,2</t>
+          <t>-2,11; 8,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 0,18</t>
+          <t>-10,13; -0,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,52</t>
+          <t>-0,42; 9,11</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 34,04</t>
+          <t>-5,08; 36,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 1,7</t>
+          <t>-31,87; 3,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 31,18</t>
+          <t>-8,41; 29,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 21,82</t>
+          <t>-16,65; 21,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 11,83</t>
+          <t>-23,78; 11,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 28,61</t>
+          <t>-4,36; 31,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 21,69</t>
+          <t>-5,37; 22,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 0,48</t>
+          <t>-24,38; -1,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 23,03</t>
+          <t>-0,91; 24,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 11,65</t>
+          <t>0,56; 12,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,85</t>
+          <t>-5,8; 5,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 44,67</t>
+          <t>2,71; 45,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 9,86</t>
+          <t>-10,66; 9,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 1,72</t>
+          <t>-19,06; 3,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 12,01</t>
+          <t>-7,63; 12,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 9,99</t>
+          <t>0,06; 9,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 3,18</t>
+          <t>-7,28; 3,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 37,62</t>
+          <t>3,22; 38,51</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 28,75</t>
+          <t>1,05; 30,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 14,17</t>
+          <t>-12,25; 14,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,34; 109,82</t>
+          <t>5,65; 115,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 19,22</t>
+          <t>-17,24; 18,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 3,4</t>
+          <t>-30,75; 6,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 24,33</t>
+          <t>-12,24; 24,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 22,51</t>
+          <t>0,03; 22,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 7,14</t>
+          <t>-14,99; 8,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 84,17</t>
+          <t>6,31; 86,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 3,67</t>
+          <t>-4,96; 3,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -0,54</t>
+          <t>-8,52; -0,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 4,94</t>
+          <t>-4,01; 4,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -0,81</t>
+          <t>-11,61; -0,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -4,52</t>
+          <t>-15,19; -4,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 26,71</t>
+          <t>-3,68; 27,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,84</t>
+          <t>-5,84; 0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,47; -3,29</t>
+          <t>-9,64; -3,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 18,78</t>
+          <t>-1,1; 20,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 8,1</t>
+          <t>-9,73; 7,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,89; -1,22</t>
+          <t>-17,07; -0,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 10,75</t>
+          <t>-7,83; 10,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,5; -1,2</t>
+          <t>-20,61; -2,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -8,86</t>
+          <t>-26,82; -8,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 50,56</t>
+          <t>-6,8; 52,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 1,79</t>
+          <t>-11,28; 1,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,99; -6,77</t>
+          <t>-18,62; -6,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 37,73</t>
+          <t>-2,16; 40,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 4,74</t>
+          <t>-9,25; 4,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,24; -0,96</t>
+          <t>-14,55; -0,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 11,38</t>
+          <t>-2,95; 10,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 9,11</t>
+          <t>-1,59; 9,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 1,79</t>
+          <t>-8,63; 2,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 4,63</t>
+          <t>-16,98; 5,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,33</t>
+          <t>-3,72; 5,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -1,51</t>
+          <t>-10,04; -1,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 5,06</t>
+          <t>-11,4; 5,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 10,83</t>
+          <t>-17,22; 10,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,96; -1,88</t>
+          <t>-27,09; -1,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 24,8</t>
+          <t>-5,61; 24,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 16,55</t>
+          <t>-2,73; 17,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 3,27</t>
+          <t>-14,26; 4,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 8,17</t>
+          <t>-28,21; 9,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 10,07</t>
+          <t>-6,38; 10,52</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,0; -2,89</t>
+          <t>-17,47; -2,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 9,58</t>
+          <t>-20,16; 9,52</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 13,19</t>
+          <t>-0,66; 12,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 9,92</t>
+          <t>-3,85; 9,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 13,42</t>
+          <t>-6,01; 13,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -1,07</t>
+          <t>-8,98; -1,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -7,45</t>
+          <t>-15,33; -6,95</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,14; -4,27</t>
+          <t>-12,73; -4,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 0,8</t>
+          <t>-6,79; 0,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,61; -5,73</t>
+          <t>-12,83; -5,39</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -3,36</t>
+          <t>-12,31; -3,38</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 96,15</t>
+          <t>-4,75; 87,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 67,57</t>
+          <t>-17,59; 65,91</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 88,63</t>
+          <t>-30,47; 86,86</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -1,73</t>
+          <t>-13,42; -1,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-23,82; -11,72</t>
+          <t>-22,98; -11,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-19,61; -6,72</t>
+          <t>-19,15; -6,75</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 1,35</t>
+          <t>-11,66; 0,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,95; -10,41</t>
+          <t>-22,37; -9,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-21,21; -6,36</t>
+          <t>-21,49; -6,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,78</t>
+          <t>-0,97; 3,94</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -1,26</t>
+          <t>-5,99; -1,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,65; 19,74</t>
+          <t>2,44; 19,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,29; -0,31</t>
+          <t>-5,28; -0,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -6,85</t>
+          <t>-11,59; -6,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 7,33</t>
+          <t>-6,56; 6,11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,13</t>
+          <t>-2,44; 1,12</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -4,74</t>
+          <t>-8,23; -4,74</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 8,31</t>
+          <t>-0,92; 9,35</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 9,11</t>
+          <t>-2,29; 9,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -2,94</t>
+          <t>-13,69; -2,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6,1; 48,45</t>
+          <t>5,52; 46,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,13; -0,55</t>
+          <t>-9,04; -0,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-20,18; -12,31</t>
+          <t>-19,95; -12,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 13,04</t>
+          <t>-11,38; 10,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,29</t>
+          <t>-4,82; 2,29</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,81; -9,62</t>
+          <t>-16,33; -9,75</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 16,82</t>
+          <t>-1,86; 18,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,32</t>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 3,03</t>
+          <t>-11,74; 2,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 1,46</t>
+          <t>-12,22; 1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 11,55</t>
+          <t>-1,58; 11,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 2,02</t>
+          <t>-13,62; 2,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,09; -7,73</t>
+          <t>-22,91; -7,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 1,33</t>
+          <t>-12,06; 1,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 0,54</t>
+          <t>-9,99; 0,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -4,21</t>
+          <t>-14,8; -4,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,9</t>
+          <t>-3,32; 5,71</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,96%</t>
+          <t>-10,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 8,37</t>
+          <t>-26,23; 6,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 3,98</t>
+          <t>-28,27; 3,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 30,99</t>
+          <t>-3,49; 30,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 5,02</t>
+          <t>-26,28; 5,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,94; -17,89</t>
+          <t>-43,48; -15,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 2,67</t>
+          <t>-22,55; 2,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 1,29</t>
+          <t>-21,63; 0,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,03; -10,6</t>
+          <t>-31,87; -10,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 14,52</t>
+          <t>-7,2; 14,0</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 12,84</t>
+          <t>-2,09; 13,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 1,16</t>
+          <t>-13,73; 0,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 10,41</t>
+          <t>-3,75; 10,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 7,89</t>
+          <t>-7,22; 8,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 4,19</t>
+          <t>-10,33; 3,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 11,42</t>
+          <t>-1,13; 11,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 8,37</t>
+          <t>-2,38; 8,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -0,23</t>
+          <t>-10,07; 0,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 9,11</t>
+          <t>-1,11; 8,33</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 36,33</t>
+          <t>-4,92; 38,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,87; 3,36</t>
+          <t>-31,6; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 29,2</t>
+          <t>-8,81; 28,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 21,7</t>
+          <t>-17,29; 21,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 11,27</t>
+          <t>-23,45; 10,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 31,43</t>
+          <t>-2,48; 30,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 22,54</t>
+          <t>-5,67; 21,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,38; -1,03</t>
+          <t>-23,64; 0,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 24,51</t>
+          <t>-2,45; 22,75</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,66</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,91</t>
+          <t>3,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 12,36</t>
+          <t>-0,04; 11,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 5,85</t>
+          <t>-6,42; 6,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 45,06</t>
+          <t>-2,95; 9,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 9,05</t>
+          <t>-10,25; 9,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 3,31</t>
+          <t>-19,83; 3,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 12,19</t>
+          <t>-8,67; 11,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 9,87</t>
+          <t>-0,39; 10,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 3,73</t>
+          <t>-7,89; 3,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 38,51</t>
+          <t>-1,54; 8,99</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 30,69</t>
+          <t>-0,15; 28,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 14,51</t>
+          <t>-13,46; 15,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,65; 115,05</t>
+          <t>-6,73; 24,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 18,05</t>
+          <t>-16,66; 18,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 6,68</t>
+          <t>-32,72; 5,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 24,78</t>
+          <t>-14,05; 22,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 22,89</t>
+          <t>-0,81; 23,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 8,47</t>
+          <t>-15,81; 6,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 86,64</t>
+          <t>-3,12; 20,24</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,17</t>
+          <t>-2,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>-0,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 3,52</t>
+          <t>-4,76; 3,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,52; -0,45</t>
+          <t>-8,65; -0,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,63</t>
+          <t>-4,73; 3,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -0,99</t>
+          <t>-11,53; -1,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,19; -4,26</t>
+          <t>-14,52; -4,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 27,18</t>
+          <t>-7,06; 2,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,74</t>
+          <t>-5,72; 0,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,64; -3,39</t>
+          <t>-9,54; -2,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 20,46</t>
+          <t>-3,6; 2,69</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>-0,1%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>-3,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>-1,09%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 7,68</t>
+          <t>-9,58; 8,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -0,89</t>
+          <t>-17,28; -0,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 10,16</t>
+          <t>-9,47; 8,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -2,04</t>
+          <t>-20,28; -2,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,82; -8,26</t>
+          <t>-25,69; -9,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 52,71</t>
+          <t>-12,48; 4,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 1,52</t>
+          <t>-10,95; 1,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,62; -6,95</t>
+          <t>-18,44; -6,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 40,84</t>
+          <t>-6,91; 5,57</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,57</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>2,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 4,68</t>
+          <t>-9,97; 4,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -0,41</t>
+          <t>-14,47; -1,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 10,87</t>
+          <t>-5,22; 9,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 9,6</t>
+          <t>-2,08; 9,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 2,37</t>
+          <t>-9,11; 1,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 5,59</t>
+          <t>-3,01; 7,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,54</t>
+          <t>-3,25; 5,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -1,46</t>
+          <t>-10,27; -1,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 5,14</t>
+          <t>-2,18; 6,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,14%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 10,43</t>
+          <t>-18,85; 10,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,09; -1,13</t>
+          <t>-26,56; -2,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 24,08</t>
+          <t>-9,63; 21,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 17,51</t>
+          <t>-3,37; 16,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 4,26</t>
+          <t>-14,53; 3,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 9,96</t>
+          <t>-4,91; 12,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 10,52</t>
+          <t>-5,68; 9,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,47; -2,78</t>
+          <t>-17,91; -2,84</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 9,52</t>
+          <t>-3,75; 11,96</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-8,52</t>
+          <t>-9,77</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-8,01</t>
+          <t>-8,43</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 12,9</t>
+          <t>-0,58; 13,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 9,62</t>
+          <t>-3,94; 10,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 13,78</t>
+          <t>-5,96; 11,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,98; -1,18</t>
+          <t>-9,11; -1,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -6,95</t>
+          <t>-15,57; -7,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,73; -4,19</t>
+          <t>-14,31; -5,18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 0,51</t>
+          <t>-7,17; 0,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,83; -5,39</t>
+          <t>-12,61; -5,56</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -3,38</t>
+          <t>-12,97; -4,52</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-13,07%</t>
+          <t>-14,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-14,3%</t>
+          <t>-15,05%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 87,11</t>
+          <t>-4,06; 90,13</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 65,91</t>
+          <t>-19,85; 70,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 86,86</t>
+          <t>-30,76; 77,51</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,42; -1,86</t>
+          <t>-13,6; -1,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-22,98; -11,16</t>
+          <t>-23,25; -11,86</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-19,15; -6,75</t>
+          <t>-21,26; -8,25</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 0,97</t>
+          <t>-12,37; 0,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-22,37; -9,84</t>
+          <t>-21,94; -9,83</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-21,49; -6,47</t>
+          <t>-22,52; -8,24</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-3,88</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>-0,56</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,94</t>
+          <t>-1,25; 3,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,99; -1,16</t>
+          <t>-6,14; -1,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,64</t>
+          <t>0,43; 5,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,37</t>
+          <t>-5,15; -0,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -6,91</t>
+          <t>-11,86; -7,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 6,11</t>
+          <t>-6,15; -1,78</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,12</t>
+          <t>-2,48; 1,15</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,23; -4,74</t>
+          <t>-8,28; -4,82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,35</t>
+          <t>-2,35; 1,2</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-3,64%</t>
+          <t>-6,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>-1,12%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 9,56</t>
+          <t>-2,8; 9,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -2,83</t>
+          <t>-13,88; -2,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5,52; 46,39</t>
+          <t>0,93; 13,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -0,64</t>
+          <t>-8,86; -0,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,95; -12,42</t>
+          <t>-20,32; -12,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 10,99</t>
+          <t>-10,55; -3,28</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 2,29</t>
+          <t>-4,94; 2,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,33; -9,75</t>
+          <t>-16,17; -9,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 18,57</t>
+          <t>-4,66; 2,47</t>
         </is>
       </c>
     </row>
